--- a/docs/artifact-studio/pinterest/artifact-studio-pinterest-60.xlsx
+++ b/docs/artifact-studio/pinterest/artifact-studio-pinterest-60.xlsx
@@ -528,56 +528,16 @@
       </c>
     </row>
     <row r="2" customFormat="1" s="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Enter image URL (required)</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>Pin title (optional, max 100)</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>Description (optional, max 500)</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>Alt text (optional, max 500)</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>Destination URL (optional)</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>Select from dropdown (required)</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>Section (optional)</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>Select: low/medium/high</t>
-        </is>
-      </c>
-      <c r="I2" s="2" t="inlineStr">
-        <is>
-          <t>Select ratio</t>
-        </is>
-      </c>
-      <c r="J2" s="2" t="inlineStr">
-        <is>
-          <t>Auto-validated</t>
-        </is>
-      </c>
+      <c r="A2" s="2" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="2" t="n"/>
+      <c r="D2" s="2" t="n"/>
+      <c r="E2" s="2" t="n"/>
+      <c r="F2" s="2" t="n"/>
+      <c r="G2" s="2" t="n"/>
+      <c r="H2" s="2" t="n"/>
+      <c r="I2" s="2" t="n"/>
+      <c r="J2" s="2" t="n"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
